--- a/data/performance/daily/signal_list_2026-08-21.xlsx
+++ b/data/performance/daily/signal_list_2026-08-21.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K63"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,12 +459,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -494,45 +495,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -553,33 +559,36 @@
         <v>2720</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>2720</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>2740</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,33 +609,36 @@
         <v>128</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>123</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>130</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-3.91</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -647,33 +659,36 @@
         <v>73</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>70</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>75</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>2.74</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-4.11</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -694,33 +709,36 @@
         <v>1655</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>1645</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1670</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>0.91</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-0.6</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -741,33 +759,36 @@
         <v>790</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>790</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>795</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -788,33 +809,36 @@
         <v>1665</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>1665</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1685</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>1.2</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -835,33 +859,36 @@
         <v>685</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>695</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>705</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>2.92</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -882,33 +909,36 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>111</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>118</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>5.36</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -929,33 +959,36 @@
         <v>86</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>85</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>89</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>3.49</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-1.16</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -976,33 +1009,36 @@
         <v>492</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>472</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>510</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>3.66</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-4.07</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1023,33 +1059,36 @@
         <v>1365</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>1375</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1380</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1070,33 +1109,36 @@
         <v>185</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>183</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>190</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>2.7</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>-1.08</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1117,33 +1159,36 @@
         <v>730.5</v>
       </c>
       <c r="D17" t="n">
-        <v>740</v>
+        <v/>
       </c>
       <c r="E17" t="n">
         <v>740</v>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>1.3</v>
+      <c r="F17" t="n">
+        <v>740</v>
       </c>
       <c r="G17" s="4" t="n">
         <v>1.3</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H17" s="4" t="n">
+        <v>1.3</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1164,33 +1209,36 @@
         <v>330</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>326</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>330</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1211,33 +1259,36 @@
         <v>825</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>810</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>830</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>0.61</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-1.82</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1258,33 +1309,36 @@
         <v>1470</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>1460</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>1480</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-0.68</v>
       </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1305,33 +1359,36 @@
         <v>1015</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>1015</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>1020</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>0.49</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1352,33 +1409,36 @@
         <v>1140</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>1160</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1180</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>3.51</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1399,33 +1459,36 @@
         <v>545</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>575</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>580</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>6.42</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>5.5</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1446,33 +1509,36 @@
         <v>126</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>125</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>132</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>4.76</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-0.79</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1493,33 +1559,36 @@
         <v>236</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>236</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>240</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>1.69</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1540,33 +1609,36 @@
         <v>71</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>68</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>71</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>-4.23</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1587,33 +1659,36 @@
         <v>615</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>615</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>625</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1634,33 +1709,36 @@
         <v>72</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>72</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>73</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>1.39</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1681,33 +1759,36 @@
         <v>358</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>344</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>372</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>3.91</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-3.91</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1728,33 +1809,36 @@
         <v>3990</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>4030</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>4040</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1775,33 +1859,36 @@
         <v>1375</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>1395</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>1405</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>2.18</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1822,33 +1909,36 @@
         <v>835</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>835</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>850</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>1.8</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1869,33 +1959,36 @@
         <v>404</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>408</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>410</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1916,33 +2009,36 @@
         <v>2340</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>2340</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>2380</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1963,33 +2059,36 @@
         <v>1105</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>1095</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>1110</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>-0.9</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2010,33 +2109,36 @@
         <v>113</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>109</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>115</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>1.77</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>-3.54</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2057,33 +2159,36 @@
         <v>62</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>59</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>63</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-4.84</v>
       </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2104,33 +2209,36 @@
         <v>115</v>
       </c>
       <c r="D38" t="n">
-        <v>117</v>
+        <v/>
       </c>
       <c r="E38" t="n">
         <v>117</v>
       </c>
-      <c r="F38" s="4" t="n">
-        <v>1.74</v>
+      <c r="F38" t="n">
+        <v>117</v>
       </c>
       <c r="G38" s="4" t="n">
         <v>1.74</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H38" s="4" t="n">
+        <v>1.74</v>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2151,33 +2259,36 @@
         <v>775</v>
       </c>
       <c r="D39" t="n">
+        <v/>
+      </c>
+      <c r="E39" t="n">
         <v>800</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>895</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="G39" s="4" t="n">
         <v>15.48</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>3.23</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2198,33 +2309,36 @@
         <v>1365</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>1370</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>1380</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>1.1</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>0.37</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2245,33 +2359,36 @@
         <v>65</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>62</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>68</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>4.62</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>-4.62</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2292,33 +2409,36 @@
         <v>181</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>184</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>185</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>2.21</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>1.66</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2339,33 +2459,36 @@
         <v>9800</v>
       </c>
       <c r="D43" t="n">
+        <v/>
+      </c>
+      <c r="E43" t="n">
         <v>9550</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>10500</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>7.14</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>-2.55</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2386,33 +2509,36 @@
         <v>515</v>
       </c>
       <c r="D44" t="n">
-        <v>535</v>
+        <v/>
       </c>
       <c r="E44" t="n">
         <v>535</v>
       </c>
-      <c r="F44" s="4" t="n">
-        <v>3.88</v>
+      <c r="F44" t="n">
+        <v>535</v>
       </c>
       <c r="G44" s="4" t="n">
         <v>3.88</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H44" s="4" t="n">
+        <v>3.88</v>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2433,33 +2559,36 @@
         <v>1915</v>
       </c>
       <c r="D45" t="n">
+        <v/>
+      </c>
+      <c r="E45" t="n">
         <v>1960</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>1980</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>3.39</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>2.35</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2480,33 +2609,36 @@
         <v>282</v>
       </c>
       <c r="D46" t="n">
+        <v/>
+      </c>
+      <c r="E46" t="n">
         <v>270</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>284</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>-4.26</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2527,33 +2659,36 @@
         <v>1140</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>1160</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>1185</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>3.95</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2574,33 +2709,36 @@
         <v>75</v>
       </c>
       <c r="D48" t="n">
+        <v/>
+      </c>
+      <c r="E48" t="n">
         <v>77</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>80</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>2.67</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2621,33 +2759,36 @@
         <v>575</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>570</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>585</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>1.74</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>-0.87</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2668,33 +2809,36 @@
         <v>115</v>
       </c>
       <c r="D50" t="n">
+        <v/>
+      </c>
+      <c r="E50" t="n">
         <v>124</v>
       </c>
-      <c r="E50" t="n">
+      <c r="F50" t="n">
         <v>148</v>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>28.7</v>
       </c>
-      <c r="G50" s="4" t="n">
+      <c r="H50" s="4" t="n">
         <v>7.83</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2715,33 +2859,36 @@
         <v>185</v>
       </c>
       <c r="D51" t="n">
+        <v/>
+      </c>
+      <c r="E51" t="n">
         <v>191</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>232</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>25.41</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>3.24</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2762,33 +2909,36 @@
         <v>69</v>
       </c>
       <c r="D52" t="n">
-        <v>75</v>
+        <v/>
       </c>
       <c r="E52" t="n">
         <v>75</v>
       </c>
-      <c r="F52" s="4" t="n">
-        <v>8.699999999999999</v>
+      <c r="F52" t="n">
+        <v>75</v>
       </c>
       <c r="G52" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H52" s="4" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2809,33 +2959,36 @@
         <v>930</v>
       </c>
       <c r="D53" t="n">
+        <v/>
+      </c>
+      <c r="E53" t="n">
         <v>915</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>935</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>-1.61</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2856,33 +3009,36 @@
         <v>159</v>
       </c>
       <c r="D54" t="n">
+        <v/>
+      </c>
+      <c r="E54" t="n">
         <v>160</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>162</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>1.89</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>0.63</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2903,33 +3059,36 @@
         <v>73</v>
       </c>
       <c r="D55" t="n">
+        <v/>
+      </c>
+      <c r="E55" t="n">
         <v>78</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>83</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>13.7</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>6.85</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2950,33 +3109,36 @@
         <v>228</v>
       </c>
       <c r="D56" t="n">
-        <v>246</v>
+        <v/>
       </c>
       <c r="E56" t="n">
         <v>246</v>
       </c>
-      <c r="F56" s="4" t="n">
-        <v>7.89</v>
+      <c r="F56" t="n">
+        <v>246</v>
       </c>
       <c r="G56" s="4" t="n">
         <v>7.89</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H56" s="4" t="n">
+        <v>7.89</v>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2997,33 +3159,36 @@
         <v>84</v>
       </c>
       <c r="D57" t="n">
+        <v/>
+      </c>
+      <c r="E57" t="n">
         <v>80</v>
       </c>
-      <c r="E57" t="n">
+      <c r="F57" t="n">
         <v>101</v>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>20.24</v>
       </c>
-      <c r="G57" s="4" t="n">
+      <c r="H57" s="4" t="n">
         <v>-4.76</v>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3044,33 +3209,36 @@
         <v>332</v>
       </c>
       <c r="D58" t="n">
-        <v>344</v>
+        <v/>
       </c>
       <c r="E58" t="n">
         <v>344</v>
       </c>
-      <c r="F58" s="4" t="n">
-        <v>3.61</v>
+      <c r="F58" t="n">
+        <v>344</v>
       </c>
       <c r="G58" s="4" t="n">
         <v>3.61</v>
       </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H58" s="4" t="n">
+        <v>3.61</v>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3091,33 +3259,36 @@
         <v>99</v>
       </c>
       <c r="D59" t="n">
+        <v/>
+      </c>
+      <c r="E59" t="n">
         <v>99</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>101</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>2.02</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3138,33 +3309,36 @@
         <v>565</v>
       </c>
       <c r="D60" t="n">
+        <v/>
+      </c>
+      <c r="E60" t="n">
         <v>565</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>585</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3185,33 +3359,36 @@
         <v>715</v>
       </c>
       <c r="D61" t="n">
-        <v>715</v>
+        <v/>
       </c>
       <c r="E61" t="n">
         <v>715</v>
       </c>
-      <c r="F61" s="4" t="n">
-        <v>0</v>
+      <c r="F61" t="n">
+        <v>715</v>
       </c>
       <c r="G61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H61" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3232,33 +3409,36 @@
         <v>8625</v>
       </c>
       <c r="D62" t="n">
+        <v/>
+      </c>
+      <c r="E62" t="n">
         <v>8650</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>8700</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>0.87</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>0.29</v>
       </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3279,33 +3459,36 @@
         <v>2560</v>
       </c>
       <c r="D63" t="n">
+        <v/>
+      </c>
+      <c r="E63" t="n">
         <v>2550</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>2580</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="G63" s="4" t="n">
         <v>0.78</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>-0.39</v>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3322,7 +3505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3330,12 +3513,13 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3365,45 +3549,50 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
+          <t>Prev</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Percentage High</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>Percentage Close</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>W/L High</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>W/L Close</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3424,33 +3613,36 @@
         <v>4020</v>
       </c>
       <c r="D5" t="n">
+        <v/>
+      </c>
+      <c r="E5" t="n">
         <v>4580</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>5025</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="H5" s="4" t="n">
         <v>13.93</v>
       </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3471,33 +3663,36 @@
         <v>146</v>
       </c>
       <c r="D6" t="n">
+        <v/>
+      </c>
+      <c r="E6" t="n">
         <v>143</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>148</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>1.37</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="H6" s="4" t="n">
         <v>-2.05</v>
       </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3518,33 +3713,36 @@
         <v>685</v>
       </c>
       <c r="D7" t="n">
+        <v/>
+      </c>
+      <c r="E7" t="n">
         <v>680</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>695</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="H7" s="4" t="n">
         <v>-0.73</v>
       </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3565,33 +3763,36 @@
         <v>128</v>
       </c>
       <c r="D8" t="n">
+        <v/>
+      </c>
+      <c r="E8" t="n">
         <v>123</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>130</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="G8" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>-3.91</v>
       </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3612,33 +3813,36 @@
         <v>73</v>
       </c>
       <c r="D9" t="n">
+        <v/>
+      </c>
+      <c r="E9" t="n">
         <v>70</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>75</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>2.74</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="H9" s="4" t="n">
         <v>-4.11</v>
       </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3659,33 +3863,36 @@
         <v>510</v>
       </c>
       <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
         <v>505</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>525</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>2.94</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="H10" s="4" t="n">
         <v>-0.98</v>
       </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3706,33 +3913,36 @@
         <v>685</v>
       </c>
       <c r="D11" t="n">
+        <v/>
+      </c>
+      <c r="E11" t="n">
         <v>695</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>705</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>2.92</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="H11" s="4" t="n">
         <v>1.46</v>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3753,33 +3963,36 @@
         <v>645</v>
       </c>
       <c r="D12" t="n">
+        <v/>
+      </c>
+      <c r="E12" t="n">
         <v>635</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>655</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="G12" s="4" t="n">
         <v>1.55</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>-1.55</v>
       </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,33 +4013,36 @@
         <v>112</v>
       </c>
       <c r="D13" t="n">
+        <v/>
+      </c>
+      <c r="E13" t="n">
         <v>111</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>118</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>5.36</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="H13" s="4" t="n">
         <v>-0.89</v>
       </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3847,33 +4063,36 @@
         <v>16175</v>
       </c>
       <c r="D14" t="n">
+        <v/>
+      </c>
+      <c r="E14" t="n">
         <v>15600</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>16475</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>1.85</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="H14" s="4" t="n">
         <v>-3.55</v>
       </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3894,33 +4113,36 @@
         <v>133</v>
       </c>
       <c r="D15" t="n">
+        <v/>
+      </c>
+      <c r="E15" t="n">
         <v>135</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>138</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>3.76</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3941,33 +4163,36 @@
         <v>1420</v>
       </c>
       <c r="D16" t="n">
+        <v/>
+      </c>
+      <c r="E16" t="n">
         <v>1440</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1475</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="G16" s="4" t="n">
         <v>3.87</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="H16" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3988,33 +4213,36 @@
         <v>550</v>
       </c>
       <c r="D17" t="n">
+        <v/>
+      </c>
+      <c r="E17" t="n">
         <v>540</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>565</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>2.73</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="H17" s="4" t="n">
         <v>-1.82</v>
       </c>
-      <c r="H17" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4035,33 +4263,36 @@
         <v>2830</v>
       </c>
       <c r="D18" t="n">
+        <v/>
+      </c>
+      <c r="E18" t="n">
         <v>2840</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>2870</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="G18" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4082,33 +4313,36 @@
         <v>492</v>
       </c>
       <c r="D19" t="n">
+        <v/>
+      </c>
+      <c r="E19" t="n">
         <v>472</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>510</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>3.66</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="H19" s="4" t="n">
         <v>-4.07</v>
       </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4129,33 +4363,36 @@
         <v>286</v>
       </c>
       <c r="D20" t="n">
+        <v/>
+      </c>
+      <c r="E20" t="n">
         <v>280</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>284</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="H20" s="4" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4176,33 +4413,36 @@
         <v>96</v>
       </c>
       <c r="D21" t="n">
+        <v/>
+      </c>
+      <c r="E21" t="n">
         <v>96</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>99</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="G21" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="H21" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4223,33 +4463,36 @@
         <v>185</v>
       </c>
       <c r="D22" t="n">
+        <v/>
+      </c>
+      <c r="E22" t="n">
         <v>183</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>190</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="G22" s="4" t="n">
         <v>2.7</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="H22" s="4" t="n">
         <v>-1.08</v>
       </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4270,33 +4513,36 @@
         <v>900</v>
       </c>
       <c r="D23" t="n">
+        <v/>
+      </c>
+      <c r="E23" t="n">
         <v>895</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>905</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="G23" s="4" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="H23" s="4" t="n">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4317,33 +4563,36 @@
         <v>180</v>
       </c>
       <c r="D24" t="n">
+        <v/>
+      </c>
+      <c r="E24" t="n">
         <v>176</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>182</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="G24" s="4" t="n">
         <v>1.11</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="H24" s="4" t="n">
         <v>-2.22</v>
       </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4364,33 +4613,36 @@
         <v>2690</v>
       </c>
       <c r="D25" t="n">
+        <v/>
+      </c>
+      <c r="E25" t="n">
         <v>2670</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>2710</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="G25" s="4" t="n">
         <v>0.74</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>-0.74</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4411,33 +4663,36 @@
         <v>1495</v>
       </c>
       <c r="D26" t="n">
+        <v/>
+      </c>
+      <c r="E26" t="n">
         <v>1500</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>1565</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="G26" s="4" t="n">
         <v>4.68</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>0.33</v>
       </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4458,33 +4713,36 @@
         <v>330</v>
       </c>
       <c r="D27" t="n">
+        <v/>
+      </c>
+      <c r="E27" t="n">
         <v>326</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>330</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="H27" s="4" t="n">
         <v>-1.21</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4505,33 +4763,36 @@
         <v>206</v>
       </c>
       <c r="D28" t="n">
+        <v/>
+      </c>
+      <c r="E28" t="n">
         <v>200</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>220</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="G28" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>-2.91</v>
       </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4552,33 +4813,36 @@
         <v>825</v>
       </c>
       <c r="D29" t="n">
+        <v/>
+      </c>
+      <c r="E29" t="n">
         <v>810</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>830</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>0.61</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="H29" s="4" t="n">
         <v>-1.82</v>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4599,33 +4863,36 @@
         <v>1470</v>
       </c>
       <c r="D30" t="n">
+        <v/>
+      </c>
+      <c r="E30" t="n">
         <v>1460</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>1480</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>0.68</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="H30" s="4" t="n">
         <v>-0.68</v>
       </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4646,33 +4913,36 @@
         <v>850</v>
       </c>
       <c r="D31" t="n">
+        <v/>
+      </c>
+      <c r="E31" t="n">
         <v>850</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>855</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>0.59</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="H31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4693,33 +4963,36 @@
         <v>1420</v>
       </c>
       <c r="D32" t="n">
+        <v/>
+      </c>
+      <c r="E32" t="n">
         <v>1390</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>1440</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="G32" s="4" t="n">
         <v>1.41</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="H32" s="4" t="n">
         <v>-2.11</v>
       </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4740,33 +5013,36 @@
         <v>1140</v>
       </c>
       <c r="D33" t="n">
+        <v/>
+      </c>
+      <c r="E33" t="n">
         <v>1160</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>1180</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>3.51</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="H33" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4787,33 +5063,36 @@
         <v>118</v>
       </c>
       <c r="D34" t="n">
+        <v/>
+      </c>
+      <c r="E34" t="n">
         <v>117</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>118</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="G34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>-0.85</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4834,33 +5113,36 @@
         <v>137</v>
       </c>
       <c r="D35" t="n">
+        <v/>
+      </c>
+      <c r="E35" t="n">
         <v>137</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>138</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="G35" s="4" t="n">
         <v>0.73</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="H35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4881,33 +5163,36 @@
         <v>236</v>
       </c>
       <c r="D36" t="n">
+        <v/>
+      </c>
+      <c r="E36" t="n">
         <v>236</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>240</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>1.69</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4928,33 +5213,36 @@
         <v>71</v>
       </c>
       <c r="D37" t="n">
+        <v/>
+      </c>
+      <c r="E37" t="n">
         <v>68</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>71</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="H37" s="4" t="n">
         <v>-4.23</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4975,33 +5263,36 @@
         <v>615</v>
       </c>
       <c r="D38" t="n">
+        <v/>
+      </c>
+      <c r="E38" t="n">
         <v>615</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>625</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="G38" s="4" t="n">
         <v>1.63</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="H38" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5022,33 +5313,36 @@
         <v>900</v>
       </c>
       <c r="D39" t="n">
-        <v>960</v>
+        <v/>
       </c>
       <c r="E39" t="n">
         <v>960</v>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>6.67</v>
+      <c r="F39" t="n">
+        <v>960</v>
       </c>
       <c r="G39" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H39" s="4" t="n">
+        <v>6.67</v>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5069,33 +5363,36 @@
         <v>428</v>
       </c>
       <c r="D40" t="n">
+        <v/>
+      </c>
+      <c r="E40" t="n">
         <v>434</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>436</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="G40" s="4" t="n">
         <v>1.87</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="H40" s="4" t="n">
         <v>1.4</v>
       </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5116,33 +5413,36 @@
         <v>610</v>
       </c>
       <c r="D41" t="n">
+        <v/>
+      </c>
+      <c r="E41" t="n">
         <v>610</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>615</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>0.82</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="H41" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5163,33 +5463,36 @@
         <v>452</v>
       </c>
       <c r="D42" t="n">
+        <v/>
+      </c>
+      <c r="E42" t="n">
         <v>446</v>
       </c>
-      <c r="E42" t="n">
+      <c r="F42" t="n">
         <v>470</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>3.98</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="H42" s="4" t="n">
         <v>-1.33</v>
       </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5210,33 +5513,36 @@
         <v>1920</v>
       </c>
       <c r="D43" t="n">
+        <v/>
+      </c>
+      <c r="E43" t="n">
         <v>1820</v>
       </c>
-      <c r="E43" t="n">
+      <c r="F43" t="n">
         <v>1970</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>2.6</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="H43" s="4" t="n">
         <v>-5.21</v>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5257,33 +5563,36 @@
         <v>850</v>
       </c>
       <c r="D44" t="n">
+        <v/>
+      </c>
+      <c r="E44" t="n">
         <v>865</v>
       </c>
-      <c r="E44" t="n">
+      <c r="F44" t="n">
         <v>900</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>5.88</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>1.76</v>
       </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5304,33 +5613,36 @@
         <v>2560</v>
       </c>
       <c r="D45" t="n">
+        <v/>
+      </c>
+      <c r="E45" t="n">
         <v>2530</v>
       </c>
-      <c r="E45" t="n">
+      <c r="F45" t="n">
         <v>2600</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="G45" s="4" t="n">
         <v>1.56</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>-1.17</v>
       </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5351,33 +5663,36 @@
         <v>404</v>
       </c>
       <c r="D46" t="n">
+        <v/>
+      </c>
+      <c r="E46" t="n">
         <v>408</v>
       </c>
-      <c r="E46" t="n">
+      <c r="F46" t="n">
         <v>410</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>1.49</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="H46" s="4" t="n">
         <v>0.99</v>
       </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5398,33 +5713,36 @@
         <v>2340</v>
       </c>
       <c r="D47" t="n">
+        <v/>
+      </c>
+      <c r="E47" t="n">
         <v>2340</v>
       </c>
-      <c r="E47" t="n">
+      <c r="F47" t="n">
         <v>2380</v>
       </c>
-      <c r="F47" s="4" t="n">
+      <c r="G47" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="G47" s="4" t="n">
+      <c r="H47" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5445,33 +5763,36 @@
         <v>113</v>
       </c>
       <c r="D48" t="n">
+        <v/>
+      </c>
+      <c r="E48" t="n">
         <v>109</v>
       </c>
-      <c r="E48" t="n">
+      <c r="F48" t="n">
         <v>115</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="G48" s="4" t="n">
         <v>1.77</v>
       </c>
-      <c r="G48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>-3.54</v>
       </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5492,33 +5813,36 @@
         <v>62</v>
       </c>
       <c r="D49" t="n">
+        <v/>
+      </c>
+      <c r="E49" t="n">
         <v>59</v>
       </c>
-      <c r="E49" t="n">
+      <c r="F49" t="n">
         <v>63</v>
       </c>
-      <c r="F49" s="4" t="n">
+      <c r="G49" s="4" t="n">
         <v>1.61</v>
       </c>
-      <c r="G49" s="4" t="n">
+      <c r="H49" s="4" t="n">
         <v>-4.84</v>
       </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5539,33 +5863,36 @@
         <v>115</v>
       </c>
       <c r="D50" t="n">
-        <v>117</v>
+        <v/>
       </c>
       <c r="E50" t="n">
         <v>117</v>
       </c>
-      <c r="F50" s="4" t="n">
-        <v>1.74</v>
+      <c r="F50" t="n">
+        <v>117</v>
       </c>
       <c r="G50" s="4" t="n">
         <v>1.74</v>
       </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H50" s="4" t="n">
+        <v>1.74</v>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5586,33 +5913,36 @@
         <v>94</v>
       </c>
       <c r="D51" t="n">
+        <v/>
+      </c>
+      <c r="E51" t="n">
         <v>94</v>
       </c>
-      <c r="E51" t="n">
+      <c r="F51" t="n">
         <v>97</v>
       </c>
-      <c r="F51" s="4" t="n">
+      <c r="G51" s="4" t="n">
         <v>3.19</v>
       </c>
-      <c r="G51" s="4" t="n">
+      <c r="H51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5633,33 +5963,36 @@
         <v>290</v>
       </c>
       <c r="D52" t="n">
+        <v/>
+      </c>
+      <c r="E52" t="n">
         <v>282</v>
       </c>
-      <c r="E52" t="n">
+      <c r="F52" t="n">
         <v>294</v>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>1.38</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="H52" s="4" t="n">
         <v>-2.76</v>
       </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5680,33 +6013,36 @@
         <v>396</v>
       </c>
       <c r="D53" t="n">
+        <v/>
+      </c>
+      <c r="E53" t="n">
         <v>394</v>
       </c>
-      <c r="E53" t="n">
+      <c r="F53" t="n">
         <v>408</v>
       </c>
-      <c r="F53" s="4" t="n">
+      <c r="G53" s="4" t="n">
         <v>3.03</v>
       </c>
-      <c r="G53" s="4" t="n">
+      <c r="H53" s="4" t="n">
         <v>-0.51</v>
       </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5727,33 +6063,36 @@
         <v>65</v>
       </c>
       <c r="D54" t="n">
+        <v/>
+      </c>
+      <c r="E54" t="n">
         <v>62</v>
       </c>
-      <c r="E54" t="n">
+      <c r="F54" t="n">
         <v>68</v>
       </c>
-      <c r="F54" s="4" t="n">
+      <c r="G54" s="4" t="n">
         <v>4.62</v>
       </c>
-      <c r="G54" s="4" t="n">
+      <c r="H54" s="4" t="n">
         <v>-4.62</v>
       </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5774,33 +6113,36 @@
         <v>346</v>
       </c>
       <c r="D55" t="n">
+        <v/>
+      </c>
+      <c r="E55" t="n">
         <v>356</v>
       </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>366</v>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="G55" s="4" t="n">
         <v>5.78</v>
       </c>
-      <c r="G55" s="4" t="n">
+      <c r="H55" s="4" t="n">
         <v>2.89</v>
       </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5821,33 +6163,36 @@
         <v>228</v>
       </c>
       <c r="D56" t="n">
+        <v/>
+      </c>
+      <c r="E56" t="n">
         <v>224</v>
       </c>
-      <c r="E56" t="n">
+      <c r="F56" t="n">
         <v>232</v>
       </c>
-      <c r="F56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="H56" s="4" t="n">
         <v>-1.75</v>
       </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5868,33 +6213,36 @@
         <v>515</v>
       </c>
       <c r="D57" t="n">
-        <v>535</v>
+        <v/>
       </c>
       <c r="E57" t="n">
         <v>535</v>
       </c>
-      <c r="F57" s="4" t="n">
-        <v>3.88</v>
+      <c r="F57" t="n">
+        <v>535</v>
       </c>
       <c r="G57" s="4" t="n">
         <v>3.88</v>
       </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H57" s="4" t="n">
+        <v>3.88</v>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5915,33 +6263,36 @@
         <v>121</v>
       </c>
       <c r="D58" t="n">
+        <v/>
+      </c>
+      <c r="E58" t="n">
         <v>123</v>
       </c>
-      <c r="E58" t="n">
+      <c r="F58" t="n">
         <v>125</v>
       </c>
-      <c r="F58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>3.31</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="H58" s="4" t="n">
         <v>1.65</v>
       </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5962,33 +6313,36 @@
         <v>216</v>
       </c>
       <c r="D59" t="n">
+        <v/>
+      </c>
+      <c r="E59" t="n">
         <v>216</v>
       </c>
-      <c r="E59" t="n">
+      <c r="F59" t="n">
         <v>222</v>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="G59" s="4" t="n">
         <v>2.78</v>
       </c>
-      <c r="G59" s="4" t="n">
+      <c r="H59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6009,33 +6363,36 @@
         <v>675</v>
       </c>
       <c r="D60" t="n">
+        <v/>
+      </c>
+      <c r="E60" t="n">
         <v>705</v>
       </c>
-      <c r="E60" t="n">
+      <c r="F60" t="n">
         <v>730</v>
       </c>
-      <c r="F60" s="4" t="n">
+      <c r="G60" s="4" t="n">
         <v>8.15</v>
       </c>
-      <c r="G60" s="4" t="n">
+      <c r="H60" s="4" t="n">
         <v>4.44</v>
       </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6056,33 +6413,36 @@
         <v>1915</v>
       </c>
       <c r="D61" t="n">
+        <v/>
+      </c>
+      <c r="E61" t="n">
         <v>1960</v>
       </c>
-      <c r="E61" t="n">
+      <c r="F61" t="n">
         <v>1980</v>
       </c>
-      <c r="F61" s="4" t="n">
+      <c r="G61" s="4" t="n">
         <v>3.39</v>
       </c>
-      <c r="G61" s="4" t="n">
+      <c r="H61" s="4" t="n">
         <v>2.35</v>
       </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6103,33 +6463,36 @@
         <v>282</v>
       </c>
       <c r="D62" t="n">
+        <v/>
+      </c>
+      <c r="E62" t="n">
         <v>270</v>
       </c>
-      <c r="E62" t="n">
+      <c r="F62" t="n">
         <v>284</v>
       </c>
-      <c r="F62" s="4" t="n">
+      <c r="G62" s="4" t="n">
         <v>0.71</v>
       </c>
-      <c r="G62" s="4" t="n">
+      <c r="H62" s="4" t="n">
         <v>-4.26</v>
       </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6150,33 +6513,36 @@
         <v>99</v>
       </c>
       <c r="D63" t="n">
+        <v/>
+      </c>
+      <c r="E63" t="n">
         <v>100</v>
       </c>
-      <c r="E63" t="n">
+      <c r="F63" t="n">
         <v>101</v>
       </c>
-      <c r="F63" s="4" t="n">
+      <c r="G63" s="4" t="n">
         <v>2.02</v>
       </c>
-      <c r="G63" s="4" t="n">
+      <c r="H63" s="4" t="n">
         <v>1.01</v>
       </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6197,33 +6563,36 @@
         <v>1140</v>
       </c>
       <c r="D64" t="n">
+        <v/>
+      </c>
+      <c r="E64" t="n">
         <v>1160</v>
       </c>
-      <c r="E64" t="n">
+      <c r="F64" t="n">
         <v>1185</v>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>3.95</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="H64" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6244,33 +6613,36 @@
         <v>75</v>
       </c>
       <c r="D65" t="n">
+        <v/>
+      </c>
+      <c r="E65" t="n">
         <v>77</v>
       </c>
-      <c r="E65" t="n">
+      <c r="F65" t="n">
         <v>80</v>
       </c>
-      <c r="F65" s="4" t="n">
+      <c r="G65" s="4" t="n">
         <v>6.67</v>
       </c>
-      <c r="G65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>2.67</v>
       </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6291,33 +6663,36 @@
         <v>79</v>
       </c>
       <c r="D66" t="n">
-        <v>86</v>
+        <v/>
       </c>
       <c r="E66" t="n">
         <v>86</v>
       </c>
-      <c r="F66" s="4" t="n">
-        <v>8.859999999999999</v>
+      <c r="F66" t="n">
+        <v>86</v>
       </c>
       <c r="G66" s="4" t="n">
         <v>8.859999999999999</v>
       </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H66" s="4" t="n">
+        <v>8.859999999999999</v>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6338,33 +6713,36 @@
         <v>2970</v>
       </c>
       <c r="D67" t="n">
+        <v/>
+      </c>
+      <c r="E67" t="n">
         <v>3070</v>
       </c>
-      <c r="E67" t="n">
+      <c r="F67" t="n">
         <v>3490</v>
       </c>
-      <c r="F67" s="4" t="n">
+      <c r="G67" s="4" t="n">
         <v>17.51</v>
       </c>
-      <c r="G67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>3.37</v>
       </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6385,33 +6763,36 @@
         <v>86</v>
       </c>
       <c r="D68" t="n">
-        <v>94</v>
+        <v/>
       </c>
       <c r="E68" t="n">
         <v>94</v>
       </c>
-      <c r="F68" s="4" t="n">
-        <v>9.300000000000001</v>
+      <c r="F68" t="n">
+        <v>94</v>
       </c>
       <c r="G68" s="4" t="n">
         <v>9.300000000000001</v>
       </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H68" s="4" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6432,33 +6813,36 @@
         <v>79</v>
       </c>
       <c r="D69" t="n">
+        <v/>
+      </c>
+      <c r="E69" t="n">
         <v>88</v>
       </c>
-      <c r="E69" t="n">
+      <c r="F69" t="n">
         <v>90</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="G69" s="4" t="n">
         <v>13.92</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="H69" s="4" t="n">
         <v>11.39</v>
       </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6479,33 +6863,36 @@
         <v>185</v>
       </c>
       <c r="D70" t="n">
+        <v/>
+      </c>
+      <c r="E70" t="n">
         <v>191</v>
       </c>
-      <c r="E70" t="n">
+      <c r="F70" t="n">
         <v>232</v>
       </c>
-      <c r="F70" s="4" t="n">
+      <c r="G70" s="4" t="n">
         <v>25.41</v>
       </c>
-      <c r="G70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>3.24</v>
       </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6526,33 +6913,36 @@
         <v>69</v>
       </c>
       <c r="D71" t="n">
-        <v>75</v>
+        <v/>
       </c>
       <c r="E71" t="n">
         <v>75</v>
       </c>
-      <c r="F71" s="4" t="n">
-        <v>8.699999999999999</v>
+      <c r="F71" t="n">
+        <v>75</v>
       </c>
       <c r="G71" s="4" t="n">
         <v>8.699999999999999</v>
       </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H71" s="4" t="n">
+        <v>8.699999999999999</v>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6573,33 +6963,36 @@
         <v>117</v>
       </c>
       <c r="D72" t="n">
+        <v/>
+      </c>
+      <c r="E72" t="n">
         <v>116</v>
       </c>
-      <c r="E72" t="n">
+      <c r="F72" t="n">
         <v>119</v>
       </c>
-      <c r="F72" s="4" t="n">
+      <c r="G72" s="4" t="n">
         <v>1.71</v>
       </c>
-      <c r="G72" s="4" t="n">
+      <c r="H72" s="4" t="n">
         <v>-0.85</v>
       </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6620,33 +7013,36 @@
         <v>930</v>
       </c>
       <c r="D73" t="n">
+        <v/>
+      </c>
+      <c r="E73" t="n">
         <v>915</v>
       </c>
-      <c r="E73" t="n">
+      <c r="F73" t="n">
         <v>935</v>
       </c>
-      <c r="F73" s="4" t="n">
+      <c r="G73" s="4" t="n">
         <v>0.54</v>
       </c>
-      <c r="G73" s="4" t="n">
+      <c r="H73" s="4" t="n">
         <v>-1.61</v>
       </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6667,33 +7063,36 @@
         <v>63</v>
       </c>
       <c r="D74" t="n">
+        <v/>
+      </c>
+      <c r="E74" t="n">
         <v>66</v>
       </c>
-      <c r="E74" t="n">
+      <c r="F74" t="n">
         <v>77</v>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="G74" s="4" t="n">
         <v>22.22</v>
       </c>
-      <c r="G74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <v>4.76</v>
       </c>
-      <c r="H74" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6714,33 +7113,36 @@
         <v>83</v>
       </c>
       <c r="D75" t="n">
+        <v/>
+      </c>
+      <c r="E75" t="n">
         <v>82</v>
       </c>
-      <c r="E75" t="n">
+      <c r="F75" t="n">
         <v>87</v>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="G75" s="4" t="n">
         <v>4.82</v>
       </c>
-      <c r="G75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>-1.2</v>
       </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6761,33 +7163,36 @@
         <v>1360</v>
       </c>
       <c r="D76" t="n">
+        <v/>
+      </c>
+      <c r="E76" t="n">
         <v>1345</v>
       </c>
-      <c r="E76" t="n">
+      <c r="F76" t="n">
         <v>1390</v>
       </c>
-      <c r="F76" s="4" t="n">
+      <c r="G76" s="4" t="n">
         <v>2.21</v>
       </c>
-      <c r="G76" s="4" t="n">
+      <c r="H76" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I76" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6808,33 +7213,36 @@
         <v>212</v>
       </c>
       <c r="D77" t="n">
+        <v/>
+      </c>
+      <c r="E77" t="n">
         <v>198</v>
       </c>
-      <c r="E77" t="n">
+      <c r="F77" t="n">
         <v>212</v>
       </c>
-      <c r="F77" s="4" t="n">
+      <c r="G77" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="4" t="n">
+      <c r="H77" s="4" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6855,33 +7263,36 @@
         <v>252</v>
       </c>
       <c r="D78" t="n">
+        <v/>
+      </c>
+      <c r="E78" t="n">
         <v>238</v>
       </c>
-      <c r="E78" t="n">
+      <c r="F78" t="n">
         <v>260</v>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="G78" s="4" t="n">
         <v>3.17</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="H78" s="4" t="n">
         <v>-5.56</v>
       </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I78" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6902,33 +7313,36 @@
         <v>73</v>
       </c>
       <c r="D79" t="n">
+        <v/>
+      </c>
+      <c r="E79" t="n">
         <v>78</v>
       </c>
-      <c r="E79" t="n">
+      <c r="F79" t="n">
         <v>83</v>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="G79" s="4" t="n">
         <v>13.7</v>
       </c>
-      <c r="G79" s="4" t="n">
+      <c r="H79" s="4" t="n">
         <v>6.85</v>
       </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6949,33 +7363,36 @@
         <v>81</v>
       </c>
       <c r="D80" t="n">
+        <v/>
+      </c>
+      <c r="E80" t="n">
         <v>82</v>
       </c>
-      <c r="E80" t="n">
+      <c r="F80" t="n">
         <v>84</v>
       </c>
-      <c r="F80" s="4" t="n">
+      <c r="G80" s="4" t="n">
         <v>3.7</v>
       </c>
-      <c r="G80" s="4" t="n">
+      <c r="H80" s="4" t="n">
         <v>1.23</v>
       </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6996,33 +7413,36 @@
         <v>125</v>
       </c>
       <c r="D81" t="n">
+        <v/>
+      </c>
+      <c r="E81" t="n">
         <v>131</v>
       </c>
-      <c r="E81" t="n">
+      <c r="F81" t="n">
         <v>136</v>
       </c>
-      <c r="F81" s="4" t="n">
+      <c r="G81" s="4" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="H81" s="4" t="n">
         <v>4.8</v>
       </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7043,33 +7463,36 @@
         <v>228</v>
       </c>
       <c r="D82" t="n">
-        <v>246</v>
+        <v/>
       </c>
       <c r="E82" t="n">
         <v>246</v>
       </c>
-      <c r="F82" s="4" t="n">
-        <v>7.89</v>
+      <c r="F82" t="n">
+        <v>246</v>
       </c>
       <c r="G82" s="4" t="n">
         <v>7.89</v>
       </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
+      <c r="H82" s="4" t="n">
+        <v>7.89</v>
       </c>
       <c r="I82" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J82" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7090,33 +7513,36 @@
         <v>84</v>
       </c>
       <c r="D83" t="n">
+        <v/>
+      </c>
+      <c r="E83" t="n">
         <v>80</v>
       </c>
-      <c r="E83" t="n">
+      <c r="F83" t="n">
         <v>101</v>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="G83" s="4" t="n">
         <v>20.24</v>
       </c>
-      <c r="G83" s="4" t="n">
+      <c r="H83" s="4" t="n">
         <v>-4.76</v>
       </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7137,33 +7563,36 @@
         <v>3930</v>
       </c>
       <c r="D84" t="n">
+        <v/>
+      </c>
+      <c r="E84" t="n">
         <v>3930</v>
       </c>
-      <c r="E84" t="n">
+      <c r="F84" t="n">
         <v>3990</v>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="G84" s="4" t="n">
         <v>1.53</v>
       </c>
-      <c r="G84" s="4" t="n">
+      <c r="H84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7184,33 +7613,36 @@
         <v>880</v>
       </c>
       <c r="D85" t="n">
+        <v/>
+      </c>
+      <c r="E85" t="n">
         <v>835</v>
       </c>
-      <c r="E85" t="n">
+      <c r="F85" t="n">
         <v>1095</v>
       </c>
-      <c r="F85" s="4" t="n">
+      <c r="G85" s="4" t="n">
         <v>24.43</v>
       </c>
-      <c r="G85" s="4" t="n">
+      <c r="H85" s="4" t="n">
         <v>-5.11</v>
       </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I85" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7231,33 +7663,36 @@
         <v>153</v>
       </c>
       <c r="D86" t="n">
+        <v/>
+      </c>
+      <c r="E86" t="n">
         <v>179</v>
       </c>
-      <c r="E86" t="n">
+      <c r="F86" t="n">
         <v>196</v>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="G86" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="G86" s="4" t="n">
+      <c r="H86" s="4" t="n">
         <v>16.99</v>
       </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J86" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7278,33 +7713,36 @@
         <v>565</v>
       </c>
       <c r="D87" t="n">
+        <v/>
+      </c>
+      <c r="E87" t="n">
         <v>565</v>
       </c>
-      <c r="E87" t="n">
+      <c r="F87" t="n">
         <v>585</v>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="G87" s="4" t="n">
         <v>3.54</v>
       </c>
-      <c r="G87" s="4" t="n">
+      <c r="H87" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7325,33 +7763,36 @@
         <v>2120</v>
       </c>
       <c r="D88" t="n">
+        <v/>
+      </c>
+      <c r="E88" t="n">
         <v>2090</v>
       </c>
-      <c r="E88" t="n">
+      <c r="F88" t="n">
         <v>2150</v>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="G88" s="4" t="n">
         <v>1.42</v>
       </c>
-      <c r="G88" s="4" t="n">
+      <c r="H88" s="4" t="n">
         <v>-1.42</v>
       </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7372,33 +7813,36 @@
         <v>715</v>
       </c>
       <c r="D89" t="n">
-        <v>715</v>
+        <v/>
       </c>
       <c r="E89" t="n">
         <v>715</v>
       </c>
-      <c r="F89" s="4" t="n">
-        <v>0</v>
+      <c r="F89" t="n">
+        <v>715</v>
       </c>
       <c r="G89" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
+      <c r="H89" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7419,33 +7863,36 @@
         <v>105</v>
       </c>
       <c r="D90" t="n">
+        <v/>
+      </c>
+      <c r="E90" t="n">
         <v>101</v>
       </c>
-      <c r="E90" t="n">
+      <c r="F90" t="n">
         <v>106</v>
       </c>
-      <c r="F90" s="4" t="n">
+      <c r="G90" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="G90" s="4" t="n">
+      <c r="H90" s="4" t="n">
         <v>-3.81</v>
       </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-08-21.xlsx
+++ b/data/performance/daily/signal_list_2026-08-21.xlsx
@@ -559,7 +559,7 @@
         <v>2720</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>2720</v>
       </c>
       <c r="E5" t="n">
         <v>2720</v>
@@ -609,7 +609,7 @@
         <v>128</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>130</v>
       </c>
       <c r="E6" t="n">
         <v>123</v>
@@ -659,7 +659,7 @@
         <v>73</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>74</v>
       </c>
       <c r="E7" t="n">
         <v>70</v>
@@ -709,7 +709,7 @@
         <v>1655</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>1670</v>
       </c>
       <c r="E8" t="n">
         <v>1645</v>
@@ -759,7 +759,7 @@
         <v>790</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>790</v>
       </c>
       <c r="E9" t="n">
         <v>790</v>
@@ -809,7 +809,7 @@
         <v>1665</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>1660</v>
       </c>
       <c r="E10" t="n">
         <v>1665</v>
@@ -859,7 +859,7 @@
         <v>685</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>700</v>
       </c>
       <c r="E11" t="n">
         <v>695</v>
@@ -909,7 +909,7 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E12" t="n">
         <v>111</v>
@@ -959,7 +959,7 @@
         <v>86</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>86</v>
       </c>
       <c r="E13" t="n">
         <v>85</v>
@@ -1009,7 +1009,7 @@
         <v>492</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>492</v>
       </c>
       <c r="E14" t="n">
         <v>472</v>
@@ -1059,7 +1059,7 @@
         <v>1365</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>1365</v>
       </c>
       <c r="E15" t="n">
         <v>1375</v>
@@ -1109,7 +1109,7 @@
         <v>185</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>186</v>
       </c>
       <c r="E16" t="n">
         <v>183</v>
@@ -1159,7 +1159,7 @@
         <v>730.5</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>735</v>
       </c>
       <c r="E17" t="n">
         <v>740</v>
@@ -1209,7 +1209,7 @@
         <v>330</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>330</v>
       </c>
       <c r="E18" t="n">
         <v>326</v>
@@ -1259,7 +1259,7 @@
         <v>825</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>825</v>
       </c>
       <c r="E19" t="n">
         <v>810</v>
@@ -1309,7 +1309,7 @@
         <v>1470</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>1475</v>
       </c>
       <c r="E20" t="n">
         <v>1460</v>
@@ -1359,7 +1359,7 @@
         <v>1015</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>1015</v>
       </c>
       <c r="E21" t="n">
         <v>1015</v>
@@ -1409,7 +1409,7 @@
         <v>1140</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>1140</v>
       </c>
       <c r="E22" t="n">
         <v>1160</v>
@@ -1459,7 +1459,7 @@
         <v>545</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>575</v>
       </c>
       <c r="E23" t="n">
         <v>575</v>
@@ -1509,7 +1509,7 @@
         <v>126</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>128</v>
       </c>
       <c r="E24" t="n">
         <v>125</v>
@@ -1559,7 +1559,7 @@
         <v>236</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>236</v>
       </c>
       <c r="E25" t="n">
         <v>236</v>
@@ -1609,7 +1609,7 @@
         <v>71</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>71</v>
       </c>
       <c r="E26" t="n">
         <v>68</v>
@@ -1659,7 +1659,7 @@
         <v>615</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>615</v>
       </c>
       <c r="E27" t="n">
         <v>615</v>
@@ -1709,7 +1709,7 @@
         <v>72</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>72</v>
       </c>
       <c r="E28" t="n">
         <v>72</v>
@@ -1759,7 +1759,7 @@
         <v>358</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>362</v>
       </c>
       <c r="E29" t="n">
         <v>344</v>
@@ -1809,7 +1809,7 @@
         <v>3990</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>4000</v>
       </c>
       <c r="E30" t="n">
         <v>4030</v>
@@ -1859,7 +1859,7 @@
         <v>1375</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>1375</v>
       </c>
       <c r="E31" t="n">
         <v>1395</v>
@@ -1909,7 +1909,7 @@
         <v>835</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>835</v>
       </c>
       <c r="E32" t="n">
         <v>835</v>
@@ -1959,7 +1959,7 @@
         <v>404</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>404</v>
       </c>
       <c r="E33" t="n">
         <v>408</v>
@@ -2009,7 +2009,7 @@
         <v>2340</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>2370</v>
       </c>
       <c r="E34" t="n">
         <v>2340</v>
@@ -2059,7 +2059,7 @@
         <v>1105</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>1110</v>
       </c>
       <c r="E35" t="n">
         <v>1095</v>
@@ -2109,7 +2109,7 @@
         <v>113</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>114</v>
       </c>
       <c r="E36" t="n">
         <v>109</v>
@@ -2159,7 +2159,7 @@
         <v>62</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>62</v>
       </c>
       <c r="E37" t="n">
         <v>59</v>
@@ -2209,7 +2209,7 @@
         <v>115</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>116</v>
       </c>
       <c r="E38" t="n">
         <v>117</v>
@@ -2259,7 +2259,7 @@
         <v>775</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>850</v>
       </c>
       <c r="E39" t="n">
         <v>800</v>
@@ -2309,7 +2309,7 @@
         <v>1365</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>1365</v>
       </c>
       <c r="E40" t="n">
         <v>1370</v>
@@ -2359,7 +2359,7 @@
         <v>65</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="E41" t="n">
         <v>62</v>
@@ -2409,7 +2409,7 @@
         <v>181</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>181</v>
       </c>
       <c r="E42" t="n">
         <v>184</v>
@@ -2459,7 +2459,7 @@
         <v>9800</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>9750</v>
       </c>
       <c r="E43" t="n">
         <v>9550</v>
@@ -2509,7 +2509,7 @@
         <v>515</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>515</v>
       </c>
       <c r="E44" t="n">
         <v>535</v>
@@ -2559,7 +2559,7 @@
         <v>1915</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>1925</v>
       </c>
       <c r="E45" t="n">
         <v>1960</v>
@@ -2609,7 +2609,7 @@
         <v>282</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>282</v>
       </c>
       <c r="E46" t="n">
         <v>270</v>
@@ -2659,7 +2659,7 @@
         <v>1140</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>1145</v>
       </c>
       <c r="E47" t="n">
         <v>1160</v>
@@ -2709,7 +2709,7 @@
         <v>75</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>75</v>
       </c>
       <c r="E48" t="n">
         <v>77</v>
@@ -2759,7 +2759,7 @@
         <v>575</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>580</v>
       </c>
       <c r="E49" t="n">
         <v>570</v>
@@ -2809,7 +2809,7 @@
         <v>115</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>116</v>
       </c>
       <c r="E50" t="n">
         <v>124</v>
@@ -2859,7 +2859,7 @@
         <v>185</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>186</v>
       </c>
       <c r="E51" t="n">
         <v>191</v>
@@ -2909,7 +2909,7 @@
         <v>69</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>75</v>
       </c>
       <c r="E52" t="n">
         <v>75</v>
@@ -2959,7 +2959,7 @@
         <v>930</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>915</v>
       </c>
       <c r="E53" t="n">
         <v>915</v>
@@ -3009,7 +3009,7 @@
         <v>159</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>159</v>
       </c>
       <c r="E54" t="n">
         <v>160</v>
@@ -3059,7 +3059,7 @@
         <v>73</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>73</v>
       </c>
       <c r="E55" t="n">
         <v>78</v>
@@ -3109,7 +3109,7 @@
         <v>228</v>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>228</v>
       </c>
       <c r="E56" t="n">
         <v>246</v>
@@ -3159,7 +3159,7 @@
         <v>84</v>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>84</v>
       </c>
       <c r="E57" t="n">
         <v>80</v>
@@ -3209,7 +3209,7 @@
         <v>332</v>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>334</v>
       </c>
       <c r="E58" t="n">
         <v>344</v>
@@ -3259,7 +3259,7 @@
         <v>99</v>
       </c>
       <c r="D59" t="n">
-        <v/>
+        <v>99</v>
       </c>
       <c r="E59" t="n">
         <v>99</v>
@@ -3309,7 +3309,7 @@
         <v>565</v>
       </c>
       <c r="D60" t="n">
-        <v/>
+        <v>570</v>
       </c>
       <c r="E60" t="n">
         <v>565</v>
@@ -3359,7 +3359,7 @@
         <v>715</v>
       </c>
       <c r="D61" t="n">
-        <v/>
+        <v>715</v>
       </c>
       <c r="E61" t="n">
         <v>715</v>
@@ -3409,7 +3409,7 @@
         <v>8625</v>
       </c>
       <c r="D62" t="n">
-        <v/>
+        <v>8625</v>
       </c>
       <c r="E62" t="n">
         <v>8650</v>
@@ -3459,7 +3459,7 @@
         <v>2560</v>
       </c>
       <c r="D63" t="n">
-        <v/>
+        <v>2560</v>
       </c>
       <c r="E63" t="n">
         <v>2550</v>
@@ -3613,7 +3613,7 @@
         <v>4020</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>4980</v>
       </c>
       <c r="E5" t="n">
         <v>4580</v>
@@ -3663,7 +3663,7 @@
         <v>146</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>147</v>
       </c>
       <c r="E6" t="n">
         <v>143</v>
@@ -3713,7 +3713,7 @@
         <v>685</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>690</v>
       </c>
       <c r="E7" t="n">
         <v>680</v>
@@ -3763,7 +3763,7 @@
         <v>128</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>130</v>
       </c>
       <c r="E8" t="n">
         <v>123</v>
@@ -3813,7 +3813,7 @@
         <v>73</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>74</v>
       </c>
       <c r="E9" t="n">
         <v>70</v>
@@ -3863,7 +3863,7 @@
         <v>510</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>511.43</v>
       </c>
       <c r="E10" t="n">
         <v>505</v>
@@ -3913,7 +3913,7 @@
         <v>685</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>700</v>
       </c>
       <c r="E11" t="n">
         <v>695</v>
@@ -3963,7 +3963,7 @@
         <v>645</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>650</v>
       </c>
       <c r="E12" t="n">
         <v>635</v>
@@ -4013,7 +4013,7 @@
         <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>113</v>
       </c>
       <c r="E13" t="n">
         <v>111</v>
@@ -4063,7 +4063,7 @@
         <v>16175</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>15925</v>
       </c>
       <c r="E14" t="n">
         <v>15600</v>
@@ -4113,7 +4113,7 @@
         <v>133</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>133</v>
       </c>
       <c r="E15" t="n">
         <v>135</v>
@@ -4163,7 +4163,7 @@
         <v>1420</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>1430</v>
       </c>
       <c r="E16" t="n">
         <v>1440</v>
@@ -4213,7 +4213,7 @@
         <v>550</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>560</v>
       </c>
       <c r="E17" t="n">
         <v>540</v>
@@ -4263,7 +4263,7 @@
         <v>2830</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>2840</v>
       </c>
       <c r="E18" t="n">
         <v>2840</v>
@@ -4313,7 +4313,7 @@
         <v>492</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>492</v>
       </c>
       <c r="E19" t="n">
         <v>472</v>
@@ -4363,7 +4363,7 @@
         <v>286</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>284</v>
       </c>
       <c r="E20" t="n">
         <v>280</v>
@@ -4413,7 +4413,7 @@
         <v>96</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>97</v>
       </c>
       <c r="E21" t="n">
         <v>96</v>
@@ -4463,7 +4463,7 @@
         <v>185</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>186</v>
       </c>
       <c r="E22" t="n">
         <v>183</v>
@@ -4513,7 +4513,7 @@
         <v>900</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>900</v>
       </c>
       <c r="E23" t="n">
         <v>895</v>
@@ -4563,7 +4563,7 @@
         <v>180</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>180</v>
       </c>
       <c r="E24" t="n">
         <v>176</v>
@@ -4613,7 +4613,7 @@
         <v>2690</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>2680</v>
       </c>
       <c r="E25" t="n">
         <v>2670</v>
@@ -4663,7 +4663,7 @@
         <v>1495</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>1565</v>
       </c>
       <c r="E26" t="n">
         <v>1500</v>
@@ -4713,7 +4713,7 @@
         <v>330</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>330</v>
       </c>
       <c r="E27" t="n">
         <v>326</v>
@@ -4763,7 +4763,7 @@
         <v>206</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>206</v>
       </c>
       <c r="E28" t="n">
         <v>200</v>
@@ -4813,7 +4813,7 @@
         <v>825</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>825</v>
       </c>
       <c r="E29" t="n">
         <v>810</v>
@@ -4863,7 +4863,7 @@
         <v>1470</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>1475</v>
       </c>
       <c r="E30" t="n">
         <v>1460</v>
@@ -4913,7 +4913,7 @@
         <v>850</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>835</v>
       </c>
       <c r="E31" t="n">
         <v>850</v>
@@ -4963,7 +4963,7 @@
         <v>1420</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>1440</v>
       </c>
       <c r="E32" t="n">
         <v>1390</v>
@@ -5013,7 +5013,7 @@
         <v>1140</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>1140</v>
       </c>
       <c r="E33" t="n">
         <v>1160</v>
@@ -5063,7 +5063,7 @@
         <v>118</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>118</v>
       </c>
       <c r="E34" t="n">
         <v>117</v>
@@ -5113,7 +5113,7 @@
         <v>137</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>138</v>
       </c>
       <c r="E35" t="n">
         <v>137</v>
@@ -5163,7 +5163,7 @@
         <v>236</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>236</v>
       </c>
       <c r="E36" t="n">
         <v>236</v>
@@ -5213,7 +5213,7 @@
         <v>71</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>71</v>
       </c>
       <c r="E37" t="n">
         <v>68</v>
@@ -5263,7 +5263,7 @@
         <v>615</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>615</v>
       </c>
       <c r="E38" t="n">
         <v>615</v>
@@ -5313,7 +5313,7 @@
         <v>900</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>930</v>
       </c>
       <c r="E39" t="n">
         <v>960</v>
@@ -5363,7 +5363,7 @@
         <v>428</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>430</v>
       </c>
       <c r="E40" t="n">
         <v>434</v>
@@ -5413,7 +5413,7 @@
         <v>610</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>610</v>
       </c>
       <c r="E41" t="n">
         <v>610</v>
@@ -5463,7 +5463,7 @@
         <v>452</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>452</v>
       </c>
       <c r="E42" t="n">
         <v>446</v>
@@ -5513,7 +5513,7 @@
         <v>1920</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>1915</v>
       </c>
       <c r="E43" t="n">
         <v>1820</v>
@@ -5563,7 +5563,7 @@
         <v>850</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>850</v>
       </c>
       <c r="E44" t="n">
         <v>865</v>
@@ -5613,7 +5613,7 @@
         <v>2560</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>2600</v>
       </c>
       <c r="E45" t="n">
         <v>2530</v>
@@ -5663,7 +5663,7 @@
         <v>404</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>404</v>
       </c>
       <c r="E46" t="n">
         <v>408</v>
@@ -5713,7 +5713,7 @@
         <v>2340</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>2370</v>
       </c>
       <c r="E47" t="n">
         <v>2340</v>
@@ -5763,7 +5763,7 @@
         <v>113</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>114</v>
       </c>
       <c r="E48" t="n">
         <v>109</v>
@@ -5813,7 +5813,7 @@
         <v>62</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>62</v>
       </c>
       <c r="E49" t="n">
         <v>59</v>
@@ -5863,7 +5863,7 @@
         <v>115</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>116</v>
       </c>
       <c r="E50" t="n">
         <v>117</v>
@@ -5913,7 +5913,7 @@
         <v>94</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>94</v>
       </c>
       <c r="E51" t="n">
         <v>94</v>
@@ -5963,7 +5963,7 @@
         <v>290</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>294</v>
       </c>
       <c r="E52" t="n">
         <v>282</v>
@@ -6013,7 +6013,7 @@
         <v>396</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>406</v>
       </c>
       <c r="E53" t="n">
         <v>394</v>
@@ -6063,7 +6063,7 @@
         <v>65</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>65</v>
       </c>
       <c r="E54" t="n">
         <v>62</v>
@@ -6113,7 +6113,7 @@
         <v>346</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>352</v>
       </c>
       <c r="E55" t="n">
         <v>356</v>
@@ -6163,7 +6163,7 @@
         <v>228</v>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>228</v>
       </c>
       <c r="E56" t="n">
         <v>224</v>
@@ -6213,7 +6213,7 @@
         <v>515</v>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>515</v>
       </c>
       <c r="E57" t="n">
         <v>535</v>
@@ -6263,7 +6263,7 @@
         <v>121</v>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>125</v>
       </c>
       <c r="E58" t="n">
         <v>123</v>
@@ -6313,7 +6313,7 @@
         <v>216</v>
       </c>
       <c r="D59" t="n">
-        <v/>
+        <v>216</v>
       </c>
       <c r="E59" t="n">
         <v>216</v>
@@ -6363,7 +6363,7 @@
         <v>675</v>
       </c>
       <c r="D60" t="n">
-        <v/>
+        <v>670</v>
       </c>
       <c r="E60" t="n">
         <v>705</v>
@@ -6413,7 +6413,7 @@
         <v>1915</v>
       </c>
       <c r="D61" t="n">
-        <v/>
+        <v>1925</v>
       </c>
       <c r="E61" t="n">
         <v>1960</v>
@@ -6463,7 +6463,7 @@
         <v>282</v>
       </c>
       <c r="D62" t="n">
-        <v/>
+        <v>282</v>
       </c>
       <c r="E62" t="n">
         <v>270</v>
@@ -6513,7 +6513,7 @@
         <v>99</v>
       </c>
       <c r="D63" t="n">
-        <v/>
+        <v>100</v>
       </c>
       <c r="E63" t="n">
         <v>100</v>
@@ -6563,7 +6563,7 @@
         <v>1140</v>
       </c>
       <c r="D64" t="n">
-        <v/>
+        <v>1145</v>
       </c>
       <c r="E64" t="n">
         <v>1160</v>
@@ -6613,7 +6613,7 @@
         <v>75</v>
       </c>
       <c r="D65" t="n">
-        <v/>
+        <v>75</v>
       </c>
       <c r="E65" t="n">
         <v>77</v>
@@ -6663,7 +6663,7 @@
         <v>79</v>
       </c>
       <c r="D66" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E66" t="n">
         <v>86</v>
@@ -6713,7 +6713,7 @@
         <v>2970</v>
       </c>
       <c r="D67" t="n">
-        <v/>
+        <v>3180</v>
       </c>
       <c r="E67" t="n">
         <v>3070</v>
@@ -6763,7 +6763,7 @@
         <v>86</v>
       </c>
       <c r="D68" t="n">
-        <v/>
+        <v>86</v>
       </c>
       <c r="E68" t="n">
         <v>94</v>
@@ -6813,7 +6813,7 @@
         <v>79</v>
       </c>
       <c r="D69" t="n">
-        <v/>
+        <v>78</v>
       </c>
       <c r="E69" t="n">
         <v>88</v>
@@ -6863,7 +6863,7 @@
         <v>185</v>
       </c>
       <c r="D70" t="n">
-        <v/>
+        <v>186</v>
       </c>
       <c r="E70" t="n">
         <v>191</v>
@@ -6913,7 +6913,7 @@
         <v>69</v>
       </c>
       <c r="D71" t="n">
-        <v/>
+        <v>75</v>
       </c>
       <c r="E71" t="n">
         <v>75</v>
@@ -6963,7 +6963,7 @@
         <v>117</v>
       </c>
       <c r="D72" t="n">
-        <v/>
+        <v>117</v>
       </c>
       <c r="E72" t="n">
         <v>116</v>
@@ -7013,7 +7013,7 @@
         <v>930</v>
       </c>
       <c r="D73" t="n">
-        <v/>
+        <v>915</v>
       </c>
       <c r="E73" t="n">
         <v>915</v>
@@ -7063,7 +7063,7 @@
         <v>63</v>
       </c>
       <c r="D74" t="n">
-        <v/>
+        <v>64</v>
       </c>
       <c r="E74" t="n">
         <v>66</v>
@@ -7113,7 +7113,7 @@
         <v>83</v>
       </c>
       <c r="D75" t="n">
-        <v/>
+        <v>83</v>
       </c>
       <c r="E75" t="n">
         <v>82</v>
@@ -7163,7 +7163,7 @@
         <v>1360</v>
       </c>
       <c r="D76" t="n">
-        <v/>
+        <v>1390</v>
       </c>
       <c r="E76" t="n">
         <v>1345</v>
@@ -7213,7 +7213,7 @@
         <v>212</v>
       </c>
       <c r="D77" t="n">
-        <v/>
+        <v>212</v>
       </c>
       <c r="E77" t="n">
         <v>198</v>
@@ -7263,7 +7263,7 @@
         <v>252</v>
       </c>
       <c r="D78" t="n">
-        <v/>
+        <v>248</v>
       </c>
       <c r="E78" t="n">
         <v>238</v>
@@ -7313,7 +7313,7 @@
         <v>73</v>
       </c>
       <c r="D79" t="n">
-        <v/>
+        <v>73</v>
       </c>
       <c r="E79" t="n">
         <v>78</v>
@@ -7363,7 +7363,7 @@
         <v>81</v>
       </c>
       <c r="D80" t="n">
-        <v/>
+        <v>83</v>
       </c>
       <c r="E80" t="n">
         <v>82</v>
@@ -7413,7 +7413,7 @@
         <v>125</v>
       </c>
       <c r="D81" t="n">
-        <v/>
+        <v>130</v>
       </c>
       <c r="E81" t="n">
         <v>131</v>
@@ -7463,7 +7463,7 @@
         <v>228</v>
       </c>
       <c r="D82" t="n">
-        <v/>
+        <v>228</v>
       </c>
       <c r="E82" t="n">
         <v>246</v>
@@ -7513,7 +7513,7 @@
         <v>84</v>
       </c>
       <c r="D83" t="n">
-        <v/>
+        <v>84</v>
       </c>
       <c r="E83" t="n">
         <v>80</v>
@@ -7563,7 +7563,7 @@
         <v>3930</v>
       </c>
       <c r="D84" t="n">
-        <v/>
+        <v>3950</v>
       </c>
       <c r="E84" t="n">
         <v>3930</v>
@@ -7613,7 +7613,7 @@
         <v>880</v>
       </c>
       <c r="D85" t="n">
-        <v/>
+        <v>1000</v>
       </c>
       <c r="E85" t="n">
         <v>835</v>
@@ -7663,7 +7663,7 @@
         <v>153</v>
       </c>
       <c r="D86" t="n">
-        <v/>
+        <v>153</v>
       </c>
       <c r="E86" t="n">
         <v>179</v>
@@ -7713,7 +7713,7 @@
         <v>565</v>
       </c>
       <c r="D87" t="n">
-        <v/>
+        <v>570</v>
       </c>
       <c r="E87" t="n">
         <v>565</v>
@@ -7763,7 +7763,7 @@
         <v>2120</v>
       </c>
       <c r="D88" t="n">
-        <v/>
+        <v>2140</v>
       </c>
       <c r="E88" t="n">
         <v>2090</v>
@@ -7813,7 +7813,7 @@
         <v>715</v>
       </c>
       <c r="D89" t="n">
-        <v/>
+        <v>715</v>
       </c>
       <c r="E89" t="n">
         <v>715</v>
@@ -7863,7 +7863,7 @@
         <v>105</v>
       </c>
       <c r="D90" t="n">
-        <v/>
+        <v>104</v>
       </c>
       <c r="E90" t="n">
         <v>101</v>
